--- a/inst/extdata/region/2026-08-10/wb_projects_gov_eap.xlsx
+++ b/inst/extdata/region/2026-08-10/wb_projects_gov_eap.xlsx
@@ -1328,9 +1328,11 @@
         <v>85</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>2025</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>45631</v>
+      </c>
       <c r="I6" s="2" t="s">
         <v>75</v>
       </c>
@@ -1350,7 +1352,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>0</v>
@@ -1362,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="V6" s="2" t="s">
         <v>35</v>
